--- a/tests/worked_examples/tariffs/flat_household_bill.xlsx
+++ b/tests/worked_examples/tariffs/flat_household_bill.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -14,7 +14,7 @@
     <definedName function="false" hidden="false" name="energy_bought_in_kwh" vbProcedure="false">Example!$B$12</definedName>
     <definedName function="false" hidden="false" name="energy_standing_in_euro" vbProcedure="false">Example!$B$18</definedName>
     <definedName function="false" hidden="false" name="energy_working_in_euro" vbProcedure="false">Example!$B$17</definedName>
-    <definedName function="false" hidden="false" name="mean_energy_price_in_euro_per_kwh" vbProcedure="false">Example!$B$20</definedName>
+    <definedName function="false" hidden="false" name="mean_working_price_in_euro_per_kwh" vbProcedure="false">Example!$B$20</definedName>
     <definedName function="false" hidden="false" name="standing_charge_in_euro_per_year" vbProcedure="false">Example!$B$14</definedName>
     <definedName function="false" hidden="false" name="supply_kind" vbProcedure="false">Example!$B$11</definedName>
     <definedName function="false" hidden="false" name="total_bill_in_euro" vbProcedure="false">Example!$B$19</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t xml:space="preserve">METADATA</t>
   </si>
@@ -128,7 +128,10 @@
     <t xml:space="preserve">total_bill_in_euro</t>
   </si>
   <si>
-    <t xml:space="preserve">mean_energy_price_in_euro_per_kwh</t>
+    <t xml:space="preserve">mean_working_price_in_euro_per_kwh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a working price: it excludes the standing charge</t>
   </si>
 </sst>
 </file>
@@ -211,12 +214,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,201 +430,204 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>3500</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <f aca="false">energy_bought_in_kwh*working_price_in_euro_per_kwh</f>
         <v>1050</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <f aca="false">standing_charge_in_euro_per_year</f>
         <v>120</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <f aca="false">energy_working_in_euro+energy_standing_in_euro</f>
         <v>1170</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <f aca="false">working_price_in_euro_per_kwh</f>
         <v>0.3</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="3" t="n">
         <v>1E-006</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
